--- a/Excel_Prep_Tough_Topics.xlsx
+++ b/Excel_Prep_Tough_Topics.xlsx
@@ -1177,7 +1177,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D6:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Not a valid status" error="Pick one: Not Started, Working or Done." promptTitle="Status" prompt="Not Started / Working / Done" type="list">
+    <dataValidation sqref="D6:D25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Not a valid status" error="Pick one: Not Started, Working or Done." type="list">
       <formula1>"Not Started,Working,Done"</formula1>
     </dataValidation>
   </dataValidations>
